--- a/docs/controlcalidadpostcampo.xlsx
+++ b/docs/controlcalidadpostcampo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brandon.mata\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23171738-A0EE-40A5-A375-76AD82B42136}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EDD44CA-6987-4434-A967-3913C87E52A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8652" xr2:uid="{4C214464-FD86-4D11-A2C3-1C6588017889}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8304" xr2:uid="{4C214464-FD86-4D11-A2C3-1C6588017889}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
@@ -86,9 +86,6 @@
     <t>distritos</t>
   </si>
   <si>
-    <t>San Juan de Miraflores</t>
-  </si>
-  <si>
     <t>Chorrillos</t>
   </si>
   <si>
@@ -144,6 +141,9 @@
   </si>
   <si>
     <t>numero de error</t>
+  </si>
+  <si>
+    <t>San Juan De Miraflores</t>
   </si>
 </sst>
 </file>
@@ -530,7 +530,8 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="11.5546875" style="4"/>
+    <col min="1" max="5" width="11.5546875" style="4"/>
+    <col min="6" max="6" width="20.44140625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="39.88671875" style="4" customWidth="1"/>
     <col min="8" max="10" width="11.5546875" style="4"/>
   </cols>
@@ -603,11 +604,12 @@
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="60.77734375" customWidth="1"/>
+    <col min="3" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>7</v>
@@ -616,7 +618,7 @@
         <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -627,10 +629,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -641,10 +643,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -655,10 +657,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -680,7 +682,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -735,66 +737,66 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="I2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H3" s="3">
         <v>1</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
